--- a/artfynd/A 27148-2026 artfynd.xlsx
+++ b/artfynd/A 27148-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88627735</v>
+        <v>88627731</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>4660</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532936.028252956</v>
+        <v>532895</v>
       </c>
       <c r="R2" t="n">
-        <v>7105824.900322831</v>
+        <v>7105877</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2020-10-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88627731</v>
+        <v>88627735</v>
       </c>
       <c r="B3" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4660</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -838,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532895.1625863673</v>
+        <v>532936</v>
       </c>
       <c r="R3" t="n">
-        <v>7105876.983146776</v>
+        <v>7105825</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,19 +851,9 @@
           <t>2020-10-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-10-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 27148-2026 artfynd.xlsx
+++ b/artfynd/A 27148-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88627731</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,8 +892,17 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88627735</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>